--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>5.14</v>
       </c>
       <c r="R33" t="n">
-        <v>8.449999999999999</v>
+        <v>7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G52" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI52"/>
+  <dimension ref="A1:BI56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46162.66666666666</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.57</v>
+        <v>4.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>3.89</v>
       </c>
       <c r="R46" t="n">
-        <v>4.96</v>
+        <v>1.76</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46162.85416666666</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46162.875</v>
+        <v>46162.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46162.875</v>
+        <v>46162.83333333334</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46162.89583333334</v>
+        <v>46162.85416666666</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46162.91666666666</v>
+        <v>46162.875</v>
       </c>
     </row>
     <row r="51">
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46162.95833333334</v>
+        <v>46162.875</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,6 +10786,794 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
+        <v>46162.89583333334</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>New Mexico United</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="3" t="n">
+        <v>46162.91666666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="3" t="n">
+        <v>46162.95833333334</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Angel City</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="3" t="n">
+        <v>46162.95833333334</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bay</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="3" t="n">
         <v>46162.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI56"/>
+  <dimension ref="A1:BI55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="R33" t="n">
-        <v>8.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10401,27 +10401,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46162.875</v>
+        <v>46162.89583333334</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46162.89583333334</v>
+        <v>46162.91666666666</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46162.91666666666</v>
+        <v>46162.95833333334</v>
       </c>
     </row>
     <row r="54">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11377,203 +11377,6 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46162.95833333334</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N56" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH56" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="3" t="n">
         <v>46162.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>5.14</v>
       </c>
       <c r="R30" t="n">
-        <v>8.449999999999999</v>
+        <v>7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.41</v>
+        <v>4.23</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.14</v>
+        <v>3.26</v>
       </c>
       <c r="R41" t="n">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="R34" t="n">
-        <v>4.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.14</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>7</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>3.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.14</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.56</v>
+        <v>1.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>5.14</v>
       </c>
       <c r="R36" t="n">
-        <v>1.93</v>
+        <v>7</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="R39" t="n">
-        <v>8.449999999999999</v>
+        <v>4.14</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="R31" t="n">
-        <v>8.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.23</v>
+        <v>1.41</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>5.14</v>
       </c>
       <c r="R42" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.01</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>4.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>4.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>8.550000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.05</v>
+        <v>7.01</v>
       </c>
       <c r="R23" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.97</v>
+        <v>5.14</v>
       </c>
       <c r="R37" t="n">
-        <v>4.14</v>
+        <v>7</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="R38" t="n">
-        <v>8.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>4.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>2.89</v>
+        <v>1.73</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.84</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.17</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>7.01</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2</v>
+        <v>2.89</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.38</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>8.449999999999999</v>
+        <v>1.93</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>4.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.73</v>
+        <v>2.89</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.5625</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.01</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.57291666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.57291666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.57291666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46162.5625</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46162.57291666666</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="26">
@@ -5476,27 +5476,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46162.57291666666</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="27">
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46162.57291666666</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.97</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>4.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="R35" t="n">
-        <v>8.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="42">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="43">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.01</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>4.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.04</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>7.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>4.14</v>
+        <v>1.93</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.23</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.26</v>
+        <v>5.14</v>
       </c>
       <c r="R35" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>7.01</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>2.89</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>4.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>8.550000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.01</v>
+        <v>5.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>2.89</v>
+        <v>2.17</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>7.35</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,70 +1992,70 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>4.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.01</v>
+        <v>3.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>2.89</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.04</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>7.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.41</v>
+        <v>3.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.14</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>1.93</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
         <v>1.93</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="R30" t="n">
-        <v>1.8</v>
+        <v>4.14</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>4.01</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>4.51</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,124 +1598,124 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U6" t="n">
         <v>3.42</v>
       </c>
-      <c r="T6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.54</v>
-      </c>
       <c r="V6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.24</v>
       </c>
-      <c r="W6" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X6" t="n">
+      <c r="AI6" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC6" t="n">
         <v>2.23</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="BD6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
+      <c r="BF6" t="n">
         <v>1.12</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1992,70 +1992,70 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>1.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.01</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>8.550000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.05</v>
+        <v>7.01</v>
       </c>
       <c r="R18" t="n">
-        <v>2.89</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.56</v>
+        <v>1.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.93</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.23</v>
+        <v>2.39</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.26</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.65</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.93</v>
+        <v>3.2</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.04</v>
+        <v>3.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6123,10 +6123,10 @@
         <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.74</v>
+        <v>3.96</v>
       </c>
       <c r="R29" t="n">
-        <v>3.91</v>
+        <v>3.72</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="R30" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.01</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>4.51</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>4.01</v>
       </c>
       <c r="R32" t="n">
-        <v>2.62</v>
+        <v>4.51</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R33" t="n">
         <v>2.14</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>3.2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.14</v>
+        <v>3.74</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>3.91</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.64</v>
+        <v>1.41</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.41</v>
+        <v>5.14</v>
       </c>
       <c r="R35" t="n">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>4.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.8</v>
+        <v>4.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.96</v>
+        <v>4.29</v>
       </c>
       <c r="R37" t="n">
-        <v>3.72</v>
+        <v>1.61</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.05</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1795,70 +1795,70 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>4.04</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>7.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>4.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>8.550000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>5.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.89</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.01</v>
+        <v>3.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>2.89</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4034,52 +4034,52 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.38</v>
+        <v>2.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.41</v>
       </c>
       <c r="R23" t="n">
-        <v>8.449999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="S23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.65</v>
+        <v>4.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="R24" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="R26" t="n">
-        <v>2.62</v>
+        <v>3.91</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.56</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.96</v>
+        <v>5.14</v>
       </c>
       <c r="R29" t="n">
-        <v>3.72</v>
+        <v>7</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.64</v>
+        <v>3.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.41</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>4.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>4.29</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>1.61</v>
       </c>
       <c r="S31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.01</v>
+        <v>3.57</v>
       </c>
       <c r="R32" t="n">
-        <v>4.51</v>
+        <v>2.14</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.57</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>3.56</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="R34" t="n">
-        <v>3.91</v>
+        <v>1.93</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>4.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="R36" t="n">
-        <v>1.8</v>
+        <v>4.14</v>
       </c>
       <c r="S36" t="n">
-        <v>5.12</v>
+        <v>2.28</v>
       </c>
       <c r="T36" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U36" t="n">
-        <v>2.46</v>
+        <v>6.42</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W36" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="X36" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB36" t="n">
         <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AE36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1.94</v>
       </c>
-      <c r="AF36" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AW36" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.43</v>
+        <v>2.8</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.42</v>
+        <v>1.65</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.29</v>
+        <v>4.01</v>
       </c>
       <c r="R37" t="n">
-        <v>1.61</v>
+        <v>4.51</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>2.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>7.01</v>
+        <v>5.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,52 +3246,52 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>4.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.04</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.2</v>
+        <v>7.01</v>
       </c>
       <c r="R17" t="n">
-        <v>8.550000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,52 +3837,52 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.26</v>
+        <v>3.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>3.72</v>
       </c>
       <c r="S24" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.96</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>3.72</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="R28" t="n">
-        <v>2.62</v>
+        <v>4.14</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.14</v>
+        <v>4.01</v>
       </c>
       <c r="R29" t="n">
-        <v>7</v>
+        <v>4.51</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3.65</v>
+        <v>4.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="R30" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.42</v>
+        <v>3.56</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.29</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.04</v>
+        <v>2.64</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.57</v>
+        <v>3.41</v>
       </c>
       <c r="R32" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>1.41</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>5.14</v>
       </c>
       <c r="R33" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.56</v>
+        <v>4.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>4.29</v>
       </c>
       <c r="R34" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>8.449999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="S35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.92</v>
+        <v>3.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.97</v>
+        <v>3.57</v>
       </c>
       <c r="R36" t="n">
-        <v>4.14</v>
+        <v>2.14</v>
       </c>
       <c r="S36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="R37" t="n">
-        <v>4.51</v>
+        <v>2.62</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G55" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI55"/>
+  <dimension ref="A1:BI54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1204,70 +1204,70 @@
         <v>6.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1401,70 +1401,70 @@
         <v>3.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46162.45833333334</v>
+        <v>46162.5</v>
       </c>
     </row>
     <row r="11">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,28 +2968,28 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -3007,22 +3007,22 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -3031,16 +3031,16 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3085,13 +3085,13 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46162.5</v>
+        <v>46162.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -3174,13 +3174,13 @@
         <v>8.550000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3189,106 +3189,106 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3371,13 +3371,13 @@
         <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3386,106 +3386,106 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>7.01</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3640,52 +3640,52 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,100 +3756,100 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.01</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.2</v>
       </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AK17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS17" t="n">
         <v>1.88</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AT17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV17" t="n">
         <v>2.95</v>
@@ -3864,25 +3864,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.3</v>
+        <v>2.23</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.23</v>
+        <v>1.81</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46162.54166666666</v>
+        <v>46162.5625</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46162.5625</v>
+        <v>46162.57291666666</v>
       </c>
     </row>
     <row r="20">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46162.57291666666</v>
+        <v>46162.58333333334</v>
       </c>
     </row>
     <row r="23">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.96</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>5.14</v>
       </c>
       <c r="R25" t="n">
-        <v>8.449999999999999</v>
+        <v>7</v>
       </c>
       <c r="S25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3.91</v>
-      </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.55</v>
+        <v>4.29</v>
       </c>
       <c r="R27" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>2.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="R28" t="n">
-        <v>4.14</v>
+        <v>2.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>6.42</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.23</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.26</v>
+        <v>3.96</v>
       </c>
       <c r="R30" t="n">
-        <v>1.8</v>
+        <v>3.72</v>
       </c>
       <c r="S30" t="n">
-        <v>5.12</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.56</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R31" t="n">
-        <v>1.93</v>
+        <v>3.91</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.41</v>
+        <v>3.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.14</v>
+        <v>3.57</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.42</v>
+        <v>3.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.29</v>
+        <v>3.55</v>
       </c>
       <c r="R34" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R35" t="n">
-        <v>3.2</v>
+        <v>4.14</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.04</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.57</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>2.14</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7643,27 +7643,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46162.58333333334</v>
+        <v>46162.625</v>
       </c>
     </row>
     <row r="38">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46162.625</v>
+        <v>46162.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46162.66666666666</v>
+        <v>46162.83333333334</v>
       </c>
     </row>
     <row r="48">
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46162.83333333334</v>
+        <v>46162.85416666666</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.57</v>
+        <v>4.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R49" t="n">
-        <v>4.96</v>
+        <v>1.69</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46162.85416666666</v>
+        <v>46162.875</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46162.875</v>
+        <v>46162.89583333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46162.89583333334</v>
+        <v>46162.91666666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,27 +10598,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46162.91666666666</v>
+        <v>46162.95833333334</v>
       </c>
     </row>
     <row r="53">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,203 +11180,6 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46162.95833333334</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bay</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="3" t="n">
         <v>46162.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AB5" t="n">
         <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.14</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM5" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI5" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AN5" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.05</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AW13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>8.550000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.27</v>
       </c>
-      <c r="AK14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AN14" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
         <v>2.28</v>
       </c>
-      <c r="AU14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.04</v>
+        <v>2.84</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI15" t="n">
         <v>3.75</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW15" t="n">
         <v>2.23</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL15" t="n">
+      <c r="AX15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>2.23</v>
       </c>
-      <c r="AM15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BA15" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>4.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.01</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.2</v>
       </c>
-      <c r="S16" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="AQ16" t="n">
         <v>1.35</v>
       </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AS16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.9</v>
       </c>
-      <c r="AT16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,100 +3756,100 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>7.01</v>
       </c>
       <c r="R17" t="n">
-        <v>2.17</v>
+        <v>1.2</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>1.64</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X17" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.75</v>
+        <v>2.76</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.23</v>
+        <v>1.13</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
         <v>2.95</v>
@@ -3864,25 +3864,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.56</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>3.91</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,22 +4938,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.39</v>
+        <v>1.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>5.14</v>
       </c>
       <c r="R23" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4962,55 +4962,55 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5022,13 +5022,13 @@
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
@@ -5037,31 +5037,31 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB23" t="n">
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.64</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.14</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>7</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.23</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.26</v>
+        <v>4.01</v>
       </c>
       <c r="R26" t="n">
-        <v>1.8</v>
+        <v>4.51</v>
       </c>
       <c r="S26" t="n">
-        <v>5.12</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.46</v>
+        <v>4.5</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>2.53</v>
+        <v>3.44</v>
       </c>
       <c r="X26" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.8</v>
+        <v>5.35</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AB26" t="n">
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.67</v>
+        <v>2.27</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.8</v>
+        <v>2.42</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.1</v>
+        <v>4.35</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.89</v>
       </c>
-      <c r="AL26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.42</v>
+        <v>3.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.29</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.41</v>
+        <v>3.96</v>
       </c>
       <c r="R28" t="n">
-        <v>2.5</v>
+        <v>3.72</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.01</v>
+        <v>3.57</v>
       </c>
       <c r="R29" t="n">
-        <v>4.51</v>
+        <v>2.14</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.96</v>
+        <v>3.41</v>
       </c>
       <c r="R30" t="n">
-        <v>3.72</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>4.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.74</v>
+        <v>4.29</v>
       </c>
       <c r="R31" t="n">
-        <v>3.91</v>
+        <v>1.61</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.04</v>
+        <v>4.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.57</v>
+        <v>3.26</v>
       </c>
       <c r="R33" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.92</v>
+        <v>3.56</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>4.14</v>
+        <v>1.93</v>
       </c>
       <c r="S35" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="U35" t="n">
-        <v>6.42</v>
+        <v>2.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.94</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AI35" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.94</v>
+        <v>3.45</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="S36" t="n">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>10.3</v>
+        <v>3.55</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="X36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AH36" t="n">
         <v>1.21</v>
       </c>
       <c r="AI36" t="n">
-        <v>7.3</v>
+        <v>6.25</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.64</v>
+        <v>1.7</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.05</v>
+        <v>1.52</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8493,124 +8493,124 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9872,70 +9872,70 @@
         <v>4.96</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10069,40 +10069,40 @@
         <v>1.69</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE49" t="n">
         <v>1.85</v>
@@ -10111,28 +10111,28 @@
         <v>1.88</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10174,19 +10174,19 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10463,40 +10463,40 @@
         <v>1.91</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE51" t="n">
         <v>1.84</v>
@@ -10505,28 +10505,28 @@
         <v>1.84</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>0</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG51" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
         <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.07</v>
+        <v>3.1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>4.14</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.61</v>
       </c>
-      <c r="AI5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.99</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X6" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AB6" t="n">
         <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>6.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>2.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.14</v>
+        <v>2.35</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM6" t="n">
         <v>1.24</v>
       </c>
-      <c r="AI6" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AN6" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.21</v>
+        <v>1.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>1.99</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>4.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2992,106 +2992,106 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS13" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AT13" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AV13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>3.05</v>
       </c>
-      <c r="AW13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>1.47</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AG14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.41</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL14" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,130 +3559,130 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.04</v>
+        <v>1.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU16" t="n">
         <v>4.2</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
+      <c r="AV16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW16" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AX16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.54</v>
       </c>
-      <c r="AL16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM16" t="n">
+      <c r="AZ16" t="n">
         <v>1.21</v>
       </c>
-      <c r="AN16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.6</v>
       </c>
-      <c r="AS16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>3.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>3.91</v>
+        <v>1.93</v>
       </c>
       <c r="S22" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="U22" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="V22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.22</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.41</v>
+        <v>3.04</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.14</v>
+        <v>3.57</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>2.14</v>
       </c>
       <c r="S23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC23" t="n">
         <v>1.78</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA23" t="n">
+      <c r="BD23" t="n">
         <v>4.6</v>
       </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
       <c r="BE23" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.39</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.64</v>
+        <v>2.97</v>
       </c>
       <c r="R24" t="n">
-        <v>2.62</v>
+        <v>4.14</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="T24" t="n">
-        <v>2.45</v>
+        <v>1.96</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>6.42</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="W24" t="n">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="X24" t="n">
-        <v>2.15</v>
+        <v>3.18</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
         <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.15</v>
+        <v>2.78</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.44</v>
+        <v>2.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.42</v>
+        <v>1.61</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.21</v>
+        <v>3.94</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.68</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.69</v>
+        <v>1.64</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC24" t="n">
-        <v>1.7</v>
+        <v>2.31</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.3</v>
+        <v>3.32</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.01</v>
+        <v>4.29</v>
       </c>
       <c r="R26" t="n">
-        <v>4.51</v>
+        <v>1.61</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>4.5</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.24</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.1</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC26" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.65</v>
+        <v>2.39</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.55</v>
+        <v>3.64</v>
       </c>
       <c r="R27" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="S27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="U27" t="n">
         <v>2.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>3.16</v>
+        <v>3.44</v>
       </c>
       <c r="X27" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AB27" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.98</v>
+        <v>5.15</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="AH27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.41</v>
       </c>
-      <c r="AI27" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AL27" t="n">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.25</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="R28" t="n">
-        <v>3.72</v>
+        <v>4.51</v>
       </c>
       <c r="S28" t="n">
-        <v>2.79</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="V28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.22</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.31</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.04</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.57</v>
+        <v>3.96</v>
       </c>
       <c r="R29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.14</v>
       </c>
-      <c r="S29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.23</v>
       </c>
-      <c r="W29" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="AK29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC29" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.29</v>
+        <v>3.26</v>
       </c>
       <c r="R31" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>5.12</v>
       </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>2.46</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.43</v>
       </c>
       <c r="W31" t="n">
-        <v>4.2</v>
+        <v>2.53</v>
       </c>
       <c r="X31" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.66</v>
-      </c>
       <c r="AG31" t="n">
-        <v>2.06</v>
+        <v>3.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.72</v>
+        <v>1.21</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.2</v>
+        <v>7.1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AN31" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.24</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC31" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.25</v>
+        <v>3.34</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.11</v>
+        <v>1.57</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.92</v>
+        <v>3.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>4.14</v>
+        <v>1.93</v>
       </c>
       <c r="S32" t="n">
-        <v>2.28</v>
+        <v>3.7</v>
       </c>
       <c r="T32" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>6.42</v>
+        <v>2.55</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.18</v>
+        <v>2.38</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.78</v>
+        <v>4.1</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.24</v>
+        <v>1.64</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.94</v>
+        <v>2.6</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AI32" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.94</v>
+        <v>3.45</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.8</v>
+        <v>1.86</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.23</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="S33" t="n">
-        <v>5.12</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="V33" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W33" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="X33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AH33" t="n">
         <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.1</v>
+        <v>6.25</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
         <v>2.15</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,55 +7129,55 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7189,13 +7189,13 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
@@ -7204,31 +7204,31 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB34" t="n">
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.56</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R35" t="n">
-        <v>1.93</v>
+        <v>3.91</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>2.19</v>
       </c>
       <c r="T35" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U35" t="n">
-        <v>2.55</v>
+        <v>4.59</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X35" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AD35" t="n">
-        <v>4.1</v>
+        <v>5.06</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.1</v>
+        <v>2.47</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.6</v>
+        <v>2.27</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.6</v>
+        <v>3.82</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>1.38</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="R36" t="n">
-        <v>3.2</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>3.55</v>
+        <v>10.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="W36" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AH36" t="n">
         <v>1.21</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ36" t="n">
         <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8296,124 +8296,124 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8493,124 +8493,124 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>4.04</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.75</v>
+        <v>7.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.25</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.41</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL15" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB15" t="n">
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>4.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.01</v>
+        <v>3.75</v>
       </c>
       <c r="R17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.2</v>
       </c>
-      <c r="S17" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="AQ17" t="n">
         <v>1.35</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR17" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AS17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.9</v>
       </c>
-      <c r="AT17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>3.96</v>
       </c>
       <c r="R22" t="n">
-        <v>1.93</v>
+        <v>3.72</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>2.79</v>
       </c>
       <c r="T22" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="U22" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.25</v>
+        <v>4.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.98</v>
+        <v>4.9</v>
       </c>
       <c r="AE22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BC22" t="n">
         <v>1.67</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BD22" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.04</v>
+        <v>3.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>2.34</v>
+        <v>2.55</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA23" t="n">
         <v>1.11</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.42</v>
+        <v>2.25</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5019,52 +5019,52 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>4.14</v>
+        <v>3.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="U24" t="n">
-        <v>6.42</v>
+        <v>3.55</v>
       </c>
       <c r="V24" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W24" t="n">
         <v>2.63</v>
       </c>
       <c r="X24" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.199999999999999</v>
+        <v>6.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.29</v>
+        <v>5.14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.61</v>
+        <v>7</v>
       </c>
       <c r="S26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z26" t="n">
         <v>4</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.05</v>
-      </c>
       <c r="AA26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE26" t="n">
         <v>1.37</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.24</v>
+        <v>2.75</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
@@ -5628,34 +5628,34 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.01</v>
+        <v>3.64</v>
       </c>
       <c r="R28" t="n">
-        <v>4.51</v>
+        <v>2.62</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
         <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
         <v>3.44</v>
       </c>
       <c r="X28" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.35</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AB28" t="n">
         <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.5</v>
+        <v>5.15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.27</v>
+        <v>2.42</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.35</v>
+        <v>3.68</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.16</v>
+        <v>2.69</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6123,37 +6123,37 @@
         <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.96</v>
+        <v>3.74</v>
       </c>
       <c r="R29" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="S29" t="n">
-        <v>2.79</v>
+        <v>2.19</v>
       </c>
       <c r="T29" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U29" t="n">
-        <v>3.28</v>
+        <v>4.59</v>
       </c>
       <c r="V29" t="n">
         <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X29" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
@@ -6162,37 +6162,37 @@
         <v>1.11</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.9</v>
+        <v>5.06</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.42</v>
+        <v>3.82</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.54</v>
+        <v>2.07</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,16 +6237,16 @@
         <v>1.11</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BD29" t="n">
         <v>5</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.64</v>
+        <v>4.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.41</v>
+        <v>4.29</v>
       </c>
       <c r="R30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.5</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.27</v>
-      </c>
       <c r="U30" t="n">
-        <v>2.71</v>
+        <v>2.16</v>
       </c>
       <c r="V30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.26</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.23</v>
       </c>
       <c r="AK30" t="n">
         <v>1.44</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="R31" t="n">
-        <v>1.8</v>
+        <v>4.14</v>
       </c>
       <c r="S31" t="n">
-        <v>5.12</v>
+        <v>2.28</v>
       </c>
       <c r="T31" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
-        <v>2.46</v>
+        <v>6.42</v>
       </c>
       <c r="V31" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB31" t="n">
         <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AE31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1.94</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AW31" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.43</v>
+        <v>2.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>4.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.93</v>
+        <v>4.51</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U32" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X32" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.3</v>
+        <v>5.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AM32" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN32" t="n">
-        <v>1.26</v>
+        <v>2.27</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,52 +6792,52 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC32" t="n">
         <v>1.84</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="S33" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>2.63</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.25</v>
+        <v>4.52</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.41</v>
+        <v>2.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.14</v>
+        <v>3.41</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>1.78</v>
+        <v>3.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="U34" t="n">
-        <v>5.6</v>
+        <v>2.71</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X34" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.15</v>
+        <v>3.84</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.75</v>
+        <v>1.36</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7189,13 +7189,13 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
@@ -7204,34 +7204,34 @@
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="R35" t="n">
-        <v>3.91</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S35" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="T35" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U35" t="n">
-        <v>4.59</v>
+        <v>10.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W35" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="X35" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AB35" t="n">
         <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.06</v>
+        <v>2.92</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="AH35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX35" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI35" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM35" t="n">
+      <c r="AY35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN35" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BC35" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="BD35" t="n">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.38</v>
+        <v>3.04</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.9</v>
+        <v>3.57</v>
       </c>
       <c r="R36" t="n">
-        <v>8.449999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="S36" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U36" t="n">
-        <v>10.3</v>
+        <v>2.34</v>
       </c>
       <c r="V36" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
-        <v>2.53</v>
+        <v>3.52</v>
       </c>
       <c r="X36" t="n">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="Z36" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC36" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AI36" t="n">
-        <v>7.3</v>
+        <v>4.05</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AN36" t="n">
-        <v>3.05</v>
+        <v>1.22</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.95</v>
       </c>
-      <c r="AX36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8296,124 +8296,124 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8690,124 +8690,124 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>6.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="R6" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.35</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>3.44</v>
+        <v>2.88</v>
       </c>
       <c r="X6" t="n">
-        <v>2.23</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
         <v>1.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>6.07</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.35</v>
+        <v>4.14</v>
       </c>
       <c r="AH6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.61</v>
       </c>
-      <c r="AI6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.99</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>14</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.01</v>
+        <v>5.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U13" t="n">
         <v>7</v>
       </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.64</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Z13" t="n">
         <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>1.08</v>
       </c>
       <c r="AD13" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.3</v>
+        <v>1.21</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.23</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AG14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.41</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL14" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.84</v>
+        <v>4.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="T15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.45</v>
       </c>
-      <c r="U15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AU15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW15" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AX15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
         <v>1.78</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BD15" t="n">
         <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.28</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>7.01</v>
       </c>
       <c r="R16" t="n">
-        <v>8.550000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="S16" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>7</v>
+        <v>1.64</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Z16" t="n">
         <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
         <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.21</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>1.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,130 +3756,130 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.04</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.73</v>
+        <v>2.89</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>2.48</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>3.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.23</v>
       </c>
       <c r="U24" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>2.63</v>
+        <v>3.16</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.95</v>
+        <v>3.98</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.25</v>
+        <v>4.52</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>2.3</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.23</v>
+        <v>2.64</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.26</v>
+        <v>3.41</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>5.12</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>2.27</v>
       </c>
       <c r="U25" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
-        <v>2.53</v>
+        <v>3.3</v>
       </c>
       <c r="X25" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.51</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.1</v>
+        <v>3.84</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AM25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF25" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.41</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.14</v>
+        <v>2.97</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>4.14</v>
       </c>
       <c r="S26" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="T26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA26" t="n">
         <v>2.8</v>
       </c>
-      <c r="U26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.58</v>
+        <v>2.31</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.18</v>
+        <v>1.51</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W28" t="n">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
         <v>2.15</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BD28" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="R29" t="n">
-        <v>3.91</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>2.19</v>
+        <v>1.83</v>
       </c>
       <c r="T29" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>4.59</v>
+        <v>10.3</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="X29" t="n">
-        <v>2.24</v>
+        <v>3.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.62</v>
+        <v>1.31</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.06</v>
+        <v>2.92</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>2.11</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.47</v>
+        <v>1.68</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.27</v>
+        <v>3.58</v>
       </c>
       <c r="AH29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX29" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI29" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM29" t="n">
+      <c r="AY29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.11</v>
-      </c>
       <c r="BC29" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="BD29" t="n">
-        <v>5</v>
+        <v>3.48</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.42</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.29</v>
+        <v>3.74</v>
       </c>
       <c r="R30" t="n">
-        <v>1.61</v>
+        <v>3.91</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>2.19</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U30" t="n">
-        <v>2.16</v>
+        <v>4.59</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W30" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="X30" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.5</v>
+        <v>5.06</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.2</v>
+        <v>3.82</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.6</v>
+        <v>2.39</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.24</v>
+        <v>2.07</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.92</v>
+        <v>2.39</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.97</v>
+        <v>3.64</v>
       </c>
       <c r="R31" t="n">
-        <v>4.14</v>
+        <v>2.62</v>
       </c>
       <c r="S31" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>2.45</v>
       </c>
       <c r="U31" t="n">
-        <v>6.42</v>
+        <v>2.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="X31" t="n">
-        <v>3.18</v>
+        <v>2.15</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AB31" t="n">
         <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.78</v>
+        <v>5.15</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.24</v>
+        <v>1.44</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.61</v>
+        <v>2.42</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.94</v>
+        <v>2.21</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="AI31" t="n">
-        <v>8.199999999999999</v>
+        <v>3.68</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.64</v>
+        <v>2.69</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.07</v>
+        <v>1.36</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.31</v>
+        <v>1.7</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.32</v>
+        <v>5.3</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.01</v>
+        <v>5.14</v>
       </c>
       <c r="R32" t="n">
-        <v>4.51</v>
+        <v>7</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="T32" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="U32" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.33</v>
+        <v>1.94</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.35</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.1</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM32" t="n">
         <v>1.13</v>
       </c>
-      <c r="AD32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN32" t="n">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6795,13 +6795,13 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
@@ -6810,34 +6810,34 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.65</v>
+        <v>4.42</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>4.29</v>
       </c>
       <c r="R33" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="W33" t="n">
-        <v>3.16</v>
+        <v>4.2</v>
       </c>
       <c r="X33" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="Z33" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD33" t="n">
         <v>5.25</v>
       </c>
-      <c r="AA33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.25</v>
-      </c>
       <c r="BE33" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.64</v>
+        <v>4.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.41</v>
+        <v>3.26</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="S34" t="n">
-        <v>3.5</v>
+        <v>5.12</v>
       </c>
       <c r="T34" t="n">
-        <v>2.27</v>
+        <v>1.99</v>
       </c>
       <c r="U34" t="n">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
       <c r="V34" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="X34" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
         <v>1.02</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.5</v>
+        <v>2.88</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.26</v>
+        <v>3.8</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.84</v>
+        <v>7.1</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.44</v>
+        <v>1.89</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AM34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.57</v>
       </c>
-      <c r="AN34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.38</v>
+        <v>3.04</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.9</v>
+        <v>3.57</v>
       </c>
       <c r="R35" t="n">
-        <v>8.449999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="S35" t="n">
-        <v>1.83</v>
+        <v>4.1</v>
       </c>
       <c r="T35" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U35" t="n">
-        <v>10.3</v>
+        <v>2.34</v>
       </c>
       <c r="V35" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="W35" t="n">
-        <v>2.53</v>
+        <v>3.52</v>
       </c>
       <c r="X35" t="n">
-        <v>3.02</v>
+        <v>2.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.31</v>
+        <v>1.59</v>
       </c>
       <c r="Z35" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.92</v>
+        <v>4.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.68</v>
+        <v>2.38</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.58</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.3</v>
+        <v>4.05</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.64</v>
+        <v>1.5</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.44</v>
+        <v>2.42</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.05</v>
+        <v>1.22</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.95</v>
       </c>
-      <c r="AX35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.57</v>
+        <v>4.01</v>
       </c>
       <c r="R36" t="n">
-        <v>2.14</v>
+        <v>4.51</v>
       </c>
       <c r="S36" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="U36" t="n">
-        <v>2.34</v>
+        <v>4.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W36" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="X36" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z36" t="n">
-        <v>5.1</v>
+        <v>5.35</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB36" t="n">
         <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AD36" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AI36" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AN36" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BF36" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7705,124 +7705,124 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8690,124 +8690,124 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
         <v>2.62</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.32</v>
+        <v>3.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AH3" t="n">
         <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.35</v>
+        <v>5.54</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1115,16 +1115,16 @@
         <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
         <v>4.15</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="S4" t="n">
         <v>1.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="U4" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1219,16 +1219,16 @@
         <v>3.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
         <v>4.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB4" t="n">
         <v>1.02</v>
@@ -1237,7 +1237,7 @@
         <v>1.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>7.05</v>
+        <v>5.41</v>
       </c>
       <c r="AE4" t="n">
         <v>1.49</v>
@@ -1246,7 +1246,7 @@
         <v>2.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH4" t="n">
         <v>1.7</v>
@@ -1255,19 +1255,19 @@
         <v>3.94</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,7 +1309,7 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BC4" t="n">
         <v>1.67</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2416,40 +2416,40 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.28</v>
       </c>
-      <c r="AU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,100 +3165,100 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Z14" t="n">
         <v>3.6</v>
       </c>
-      <c r="R14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AA14" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.8</v>
+        <v>6.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AI14" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.23</v>
+        <v>3.65</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
         <v>2.95</v>
@@ -3273,25 +3273,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,28 +3362,28 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.04</v>
+        <v>4.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="U15" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X15" t="n">
         <v>2.28</v>
@@ -3392,103 +3392,103 @@
         <v>1.55</v>
       </c>
       <c r="Z15" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.13</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.18</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AS15" t="n">
         <v>1.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AX15" t="n">
         <v>1.72</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,100 +3559,100 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>2.84</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.01</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.2</v>
       </c>
-      <c r="S16" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="AK16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS16" t="n">
         <v>1.88</v>
       </c>
-      <c r="AH16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AT16" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV16" t="n">
         <v>2.95</v>
@@ -3667,25 +3667,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>2.23</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.23</v>
+        <v>1.81</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,130 +3756,130 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>3.05</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AW17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -3962,70 +3962,70 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Hammarby</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4822,52 +4822,52 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.56</v>
+        <v>1.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.93</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U23" t="n">
+        <v>9</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
         <v>3.7</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA23" t="n">
         <v>4.6</v>
       </c>
-      <c r="AJ23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.84</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.65</v>
+        <v>2.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.93</v>
+        <v>2.09</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="U24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL24" t="n">
         <v>2.5</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.64</v>
+        <v>4.27</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="V25" t="n">
-        <v>1.26</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>3.3</v>
+        <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.5</v>
+        <v>3.01</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.26</v>
+        <v>3.77</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.51</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.84</v>
+        <v>6.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.23</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="AM25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AN25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.97</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,37 +5529,37 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>4.14</v>
+        <v>4.8</v>
       </c>
       <c r="S26" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U26" t="n">
-        <v>6.42</v>
+        <v>6.53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="X26" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
         <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
         <v>1.01</v>
@@ -5568,40 +5568,40 @@
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.02</v>
       </c>
       <c r="AK26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.07</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,16 +5646,16 @@
         <v>1.26</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="BD26" t="n">
         <v>3.32</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R28" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="S28" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="W28" t="n">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.95</v>
+        <v>4.63</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>1.59</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.64</v>
+        <v>2.32</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AI28" t="n">
-        <v>6.25</v>
+        <v>4.3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC28" t="n">
         <v>1.82</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>8.449999999999999</v>
+        <v>2.59</v>
       </c>
       <c r="S29" t="n">
-        <v>1.83</v>
+        <v>2.79</v>
       </c>
       <c r="T29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X29" t="n">
         <v>2.2</v>
       </c>
-      <c r="U29" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.02</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.31</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>2.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="R30" t="n">
-        <v>3.91</v>
+        <v>2.02</v>
       </c>
       <c r="S30" t="n">
-        <v>2.19</v>
+        <v>3.6</v>
       </c>
       <c r="T30" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="U30" t="n">
-        <v>4.59</v>
+        <v>2.5</v>
       </c>
       <c r="V30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.22</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6514,40 +6514,40 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.39</v>
+        <v>2.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="S31" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="T31" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="U31" t="n">
         <v>2.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W31" t="n">
-        <v>3.44</v>
+        <v>3.75</v>
       </c>
       <c r="X31" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AB31" t="n">
         <v>1.02</v>
@@ -6556,22 +6556,22 @@
         <v>1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AE31" t="n">
         <v>1.44</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="AJ31" t="n">
         <v>1.21</v>
@@ -6586,7 +6586,7 @@
         <v>1.26</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6631,13 +6631,13 @@
         <v>1.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BD31" t="n">
         <v>5.3</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BF31" t="n">
         <v>1.29</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.14</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="S32" t="n">
-        <v>1.78</v>
+        <v>2.21</v>
       </c>
       <c r="T32" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="U32" t="n">
-        <v>5.6</v>
+        <v>4.54</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X32" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="Z32" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.75</v>
+        <v>5.04</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.75</v>
+        <v>2.06</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6795,13 +6795,13 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
@@ -6810,34 +6810,34 @@
         <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6908,16 +6908,16 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.29</v>
+        <v>3.8</v>
       </c>
       <c r="R33" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T33" t="n">
         <v>2.5</v>
@@ -6956,7 +6956,7 @@
         <v>1.37</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AG33" t="n">
         <v>2.06</v>
@@ -6968,7 +6968,7 @@
         <v>3.2</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK33" t="n">
         <v>1.44</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>4.23</v>
+        <v>1.36</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.26</v>
+        <v>4.6</v>
       </c>
       <c r="R34" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH34" t="n">
         <v>1.8</v>
       </c>
-      <c r="S34" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U34" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC34" t="n">
+      <c r="AI34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
         <v>1.35</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AS34" t="n">
-        <v>2.33</v>
+        <v>1.56</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.05</v>
+        <v>1.2</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.43</v>
+        <v>4.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.34</v>
+        <v>5.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.57</v>
+        <v>2.21</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.11</v>
+        <v>1.37</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7302,22 +7302,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="S35" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U35" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="V35" t="n">
         <v>1.23</v>
@@ -7332,7 +7332,7 @@
         <v>1.59</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AA35" t="n">
         <v>1.11</v>
@@ -7341,28 +7341,28 @@
         <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
         <v>1.5</v>
@@ -7416,13 +7416,13 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="BE35" t="n">
         <v>1.95</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.65</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.01</v>
+        <v>3.2</v>
       </c>
       <c r="R36" t="n">
-        <v>4.51</v>
+        <v>3.2</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="T36" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U36" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="V36" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>3.44</v>
+        <v>2.63</v>
       </c>
       <c r="X36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z36" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S37" t="n">
-        <v>5.8</v>
+        <v>3.73</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="X37" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.11</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BC37" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="R48" t="n">
-        <v>4.96</v>
+        <v>5.6</v>
       </c>
       <c r="S48" t="n">
         <v>2.06</v>
@@ -9890,7 +9890,7 @@
         <v>2.45</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z48" t="n">
         <v>6</v>
@@ -9908,7 +9908,7 @@
         <v>3.68</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF48" t="n">
         <v>2.07</v>
@@ -9926,10 +9926,10 @@
         <v>1.11</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AM48" t="n">
         <v>1.17</v>
@@ -10069,25 +10069,25 @@
         <v>1.69</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="T49" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="U49" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="V49" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W49" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="X49" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z49" t="n">
         <v>6.5</v>
@@ -10102,19 +10102,19 @@
         <v>1.19</v>
       </c>
       <c r="AD49" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AI49" t="n">
         <v>4.9</v>
@@ -10132,7 +10132,7 @@
         <v>1.22</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -10177,13 +10177,13 @@
         <v>1.17</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BD49" t="n">
         <v>4.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="BF49" t="n">
         <v>1.22</v>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.49</v>
+        <v>3.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="S51" t="n">
         <v>3.9</v>
@@ -10469,7 +10469,7 @@
         <v>2.2</v>
       </c>
       <c r="U51" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V51" t="n">
         <v>1.33</v>
@@ -10499,10 +10499,10 @@
         <v>3.34</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
         <v>3.05</v>
@@ -10511,10 +10511,10 @@
         <v>1.28</v>
       </c>
       <c r="AI51" t="n">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AK51" t="n">
         <v>1.73</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV13" t="n">
         <v>3.05</v>
       </c>
-      <c r="R13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AW13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.6</v>
       </c>
-      <c r="AG13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.28</v>
-      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.49</v>
+        <v>2.17</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>9.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.35</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>2.13</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>4.45</v>
+        <v>3.28</v>
       </c>
       <c r="X14" t="n">
-        <v>1.94</v>
+        <v>2.28</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AB14" t="n">
         <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AD14" t="n">
-        <v>6.85</v>
+        <v>4.4</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AF14" t="n">
-        <v>3.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AM14" t="n">
-        <v>3.65</v>
+        <v>1.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="BB14" t="n">
         <v>1.13</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>4.55</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>6.35</v>
       </c>
       <c r="R15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.6</v>
       </c>
-      <c r="S15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.13</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>3.28</v>
+        <v>4.4</v>
       </c>
       <c r="X15" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AB15" t="n">
         <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.4</v>
+        <v>6.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="BB15" t="n">
         <v>1.13</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.55</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,130 +3559,130 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>2</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,130 +3756,130 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.28</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>8.550000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="S17" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV17" t="n">
         <v>2.95</v>
       </c>
-      <c r="U17" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AW17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
         <v>2</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.17</v>
       </c>
       <c r="BF17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.95</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="AF22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.15</v>
       </c>
-      <c r="U22" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.98</v>
-      </c>
       <c r="BD22" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.29</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>1.95</v>
       </c>
       <c r="S23" t="n">
-        <v>1.83</v>
+        <v>4.16</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>2.57</v>
       </c>
       <c r="V23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.43</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.95</v>
+        <v>3.62</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AF23" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS23" t="n">
         <v>1.68</v>
       </c>
-      <c r="AG23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS23" t="n">
+      <c r="AT23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>2.17</v>
       </c>
-      <c r="AT23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BA23" t="n">
-        <v>4.6</v>
+        <v>1.86</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.48</v>
+        <v>4.15</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.87</v>
+        <v>1.61</v>
       </c>
       <c r="Q24" t="n">
         <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.09</v>
+        <v>4.8</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.27</v>
+        <v>1.97</v>
       </c>
       <c r="U24" t="n">
-        <v>2.73</v>
+        <v>6.53</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
         <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.5</v>
+        <v>2.84</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.26</v>
+        <v>3.9</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.51</v>
+        <v>1.18</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.84</v>
+        <v>8.1</v>
       </c>
       <c r="AJ24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.23</v>
       </c>
-      <c r="AK24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL24" t="n">
+      <c r="AN24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
         <v>2.5</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AV24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC24" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.7</v>
+        <v>3.32</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>4.8</v>
+        <v>1.83</v>
       </c>
       <c r="S26" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.25</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U26" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>5.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
         <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.84</v>
+        <v>4.95</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.16</v>
+        <v>1.54</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.9</v>
+        <v>2.28</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.1</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.65</v>
+        <v>2.42</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.32</v>
+        <v>4.95</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,13 +5810,13 @@
         <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU27" t="n">
         <v>0</v>
@@ -5825,34 +5825,34 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>2.98</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI28" t="n">
         <v>4.45</v>
       </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.27</v>
+        <v>1.3</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.23</v>
+        <v>3.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>2.59</v>
+        <v>1.78</v>
       </c>
       <c r="S29" t="n">
-        <v>2.79</v>
+        <v>3.75</v>
       </c>
       <c r="T29" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>3.28</v>
+        <v>2.16</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="X29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z29" t="n">
-        <v>5</v>
+        <v>4.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BC29" t="n">
         <v>1.67</v>
       </c>
       <c r="BD29" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.98</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>2.02</v>
+        <v>3.8</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>2.21</v>
       </c>
       <c r="T30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.23</v>
       </c>
-      <c r="U30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.36</v>
-      </c>
       <c r="Y30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK30" t="n">
         <v>1.51</v>
       </c>
-      <c r="Z30" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AL30" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.25</v>
+        <v>4.95</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="R32" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="S32" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="T32" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="U32" t="n">
-        <v>4.54</v>
+        <v>9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W32" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="X32" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
         <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.04</v>
+        <v>2.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="AH32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM32" t="n">
+      <c r="AY32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.12</v>
-      </c>
       <c r="BC32" t="n">
-        <v>1.74</v>
+        <v>2.24</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.95</v>
+        <v>3.48</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>7.3</v>
+        <v>4.45</v>
       </c>
       <c r="S34" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="V34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
         <v>1.18</v>
       </c>
-      <c r="W34" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY34" t="n">
+      <c r="BC34" t="n">
         <v>1.82</v>
       </c>
-      <c r="AZ34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BD34" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,28 +7302,28 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q35" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R35" t="n">
-        <v>1.83</v>
+        <v>2.09</v>
       </c>
       <c r="S35" t="n">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="U35" t="n">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="V35" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W35" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="X35" t="n">
         <v>2.25</v>
@@ -7332,49 +7332,49 @@
         <v>1.59</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB35" t="n">
         <v>1.02</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC35" t="n">
         <v>1.77</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="S36" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="T36" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="U36" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W36" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.95</v>
+        <v>5.33</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="AI36" t="n">
-        <v>6.25</v>
+        <v>3.42</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.82</v>
+        <v>2.69</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>3.73</v>
+        <v>5.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="V37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC37" t="n">
         <v>1.2</v>
       </c>
-      <c r="W37" t="n">
-        <v>4</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AD37" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="AI37" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AL37" t="n">
-        <v>2.33</v>
+        <v>1.95</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.77</v>
+        <v>1.4</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7902,124 +7902,124 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
@@ -8977,34 +8977,34 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q5" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R5" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="S5" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="T5" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="V5" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>3.44</v>
+        <v>2.55</v>
       </c>
       <c r="X5" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
         <v>1.02</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2840,7 +2840,7 @@
         <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="AN12" t="n">
         <v>1.03</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.96</v>
+        <v>3.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.28</v>
       </c>
-      <c r="AU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.17</v>
+        <v>1.49</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU14" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="AV14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
         <v>1.6</v>
       </c>
-      <c r="S14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BD14" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,130 +3559,130 @@
         </is>
       </c>
       <c r="P16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF16" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V16" t="n">
+      <c r="AG16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.41</v>
       </c>
-      <c r="W16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL16" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.13</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X17" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.14</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.55</v>
+        <v>2.18</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3840,49 +3840,49 @@
         <v>1.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AU17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.23</v>
+        <v>3.45</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>4.16</v>
       </c>
       <c r="T22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT22" t="n">
         <v>2.06</v>
       </c>
-      <c r="U22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="S23" t="n">
-        <v>4.16</v>
+        <v>2.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="U23" t="n">
-        <v>2.57</v>
+        <v>6.53</v>
       </c>
       <c r="V23" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.62</v>
+        <v>2.84</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AX23" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.15</v>
+        <v>3.32</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.61</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG24" t="n">
         <v>3.4</v>
       </c>
-      <c r="R24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.27</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.82</v>
+        <v>4.45</v>
       </c>
       <c r="S25" t="n">
-        <v>4.75</v>
+        <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="U25" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>2.53</v>
+        <v>3.36</v>
       </c>
       <c r="X25" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.01</v>
+        <v>4.63</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.77</v>
+        <v>2.38</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AK25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.91</v>
       </c>
-      <c r="AL25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.57</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,80 +5529,80 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.4</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.83</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
-        <v>4.22</v>
+        <v>2.79</v>
       </c>
       <c r="T26" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="U26" t="n">
-        <v>2.29</v>
+        <v>3.28</v>
       </c>
       <c r="V26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.23</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE26" t="n">
+      <c r="AK26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.54</v>
       </c>
-      <c r="AF26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
         <v>1.36</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R27" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="U27" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AD27" t="n">
-        <v>6.34</v>
+        <v>3.01</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.06</v>
+        <v>3.77</v>
       </c>
       <c r="AH27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW27" t="n">
         <v>1.78</v>
       </c>
-      <c r="AI27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK27" t="n">
+      <c r="AX27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>2.21</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.98</v>
+        <v>1.29</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.02</v>
+        <v>11</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="T28" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="U28" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
-        <v>3.16</v>
+        <v>2.53</v>
       </c>
       <c r="X28" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.98</v>
+        <v>2.95</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.45</v>
+        <v>7.3</v>
       </c>
       <c r="AJ28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.14</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AN28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE28" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q29" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R29" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="W29" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="X29" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AD29" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK29" t="n">
         <v>1.44</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.25</v>
+        <v>4.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="S30" t="n">
-        <v>2.21</v>
+        <v>1.79</v>
       </c>
       <c r="T30" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="U30" t="n">
-        <v>4.54</v>
+        <v>5.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W30" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="X30" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.04</v>
+        <v>6.34</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.45</v>
+        <v>2.72</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.06</v>
+        <v>2.94</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6401,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU30" t="n">
         <v>0</v>
@@ -6416,34 +6416,34 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.74</v>
+        <v>1.59</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.29</v>
+        <v>3.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>11</v>
+        <v>1.78</v>
       </c>
       <c r="S32" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>9</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="X32" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.34</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>4.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AB32" t="n">
         <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.68</v>
+        <v>2.7</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>1.72</v>
       </c>
       <c r="AI32" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.64</v>
+        <v>1.44</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.05</v>
+        <v>1.24</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.24</v>
+        <v>1.67</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.48</v>
+        <v>5.25</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W34" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W34" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z34" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB34" t="n">
         <v>1.02</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.63</v>
+        <v>4.95</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X36" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W36" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Y36" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z36" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB36" t="n">
         <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.33</v>
+        <v>5.04</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BD36" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7705,124 +7705,124 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8493,124 +8493,124 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
         <v>0</v>
@@ -8977,34 +8977,34 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9356,13 +9356,13 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU45" t="n">
         <v>0</v>
@@ -9371,34 +9371,34 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -10111,10 +10111,10 @@
         <v>2.01</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AI49" t="n">
         <v>4.9</v>
@@ -10129,10 +10129,10 @@
         <v>2</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>2.89</v>
+        <v>1.6</v>
       </c>
       <c r="S13" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>3.4</v>
+        <v>2.13</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>2.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.7</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.79</v>
+        <v>2.18</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>2.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>8.550000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="S14" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV14" t="n">
         <v>2.95</v>
       </c>
-      <c r="U14" t="n">
-        <v>7</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="AW14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
         <v>2</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2.17</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.35</v>
+        <v>5.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.28</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U15" t="n">
         <v>7</v>
       </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>1.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA15" t="n">
         <v>1.19</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>1.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>6.75</v>
+        <v>5.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AF15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>3.05</v>
       </c>
-      <c r="AG15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AW15" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.3</v>
+        <v>1.21</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.23</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,100 +3559,100 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q16" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z16" t="n">
         <v>3.6</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.8</v>
+        <v>6.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.75</v>
+        <v>2.85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>3.6</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
         <v>2.95</v>
@@ -3667,25 +3667,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.6</v>
       </c>
-      <c r="S17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AG17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.95</v>
+        <v>4.8</v>
       </c>
       <c r="S22" t="n">
-        <v>4.16</v>
+        <v>2.25</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>2.57</v>
+        <v>6.53</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.62</v>
+        <v>2.84</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.83</v>
+        <v>3.9</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.6</v>
+        <v>8.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.68</v>
+        <v>2.85</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.55</v>
+        <v>1.58</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.15</v>
+        <v>3.32</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.61</v>
+        <v>2.87</v>
       </c>
       <c r="Q23" t="n">
         <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>4.8</v>
+        <v>2.09</v>
       </c>
       <c r="S23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.25</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AB23" t="n">
         <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="AI23" t="n">
-        <v>8.1</v>
+        <v>3.84</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="U24" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.95</v>
+        <v>5.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.25</v>
+        <v>3.42</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>1.23</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.82</v>
+        <v>2.69</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R25" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W25" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z25" t="n">
-        <v>5.3</v>
+        <v>5.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.63</v>
+        <v>4.95</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AI25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.23</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.33</v>
+        <v>5.04</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.54</v>
+        <v>2.06</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="S27" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.53</v>
+        <v>4.2</v>
       </c>
       <c r="X27" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.01</v>
+        <v>5.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>1.37</v>
       </c>
       <c r="AF27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AG27" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.23</v>
-      </c>
       <c r="BD27" t="n">
-        <v>3.34</v>
+        <v>5.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI28" t="n">
         <v>4.3</v>
       </c>
-      <c r="R28" t="n">
-        <v>11</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U28" t="n">
-        <v>9</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>7.3</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.47</v>
+        <v>2.17</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AN28" t="n">
-        <v>3.05</v>
+        <v>2.27</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.48</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.87</v>
+        <v>1.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>2.09</v>
+        <v>5.75</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>1.79</v>
       </c>
       <c r="T29" t="n">
-        <v>2.27</v>
+        <v>2.64</v>
       </c>
       <c r="U29" t="n">
-        <v>2.73</v>
+        <v>5.95</v>
       </c>
       <c r="V29" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="X29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX29" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AY29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC29" t="n">
         <v>1.59</v>
       </c>
-      <c r="Z29" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BD29" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.97</v>
+        <v>2.21</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="R30" t="n">
-        <v>5.75</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="T30" t="n">
-        <v>2.64</v>
+        <v>2.13</v>
       </c>
       <c r="U30" t="n">
-        <v>5.95</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="W30" t="n">
-        <v>3.98</v>
+        <v>2.53</v>
       </c>
       <c r="X30" t="n">
-        <v>2.07</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.71</v>
+        <v>1.34</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AB30" t="n">
         <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AD30" t="n">
-        <v>6.34</v>
+        <v>2.95</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.72</v>
+        <v>1.68</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.78</v>
+        <v>1.21</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.45</v>
+        <v>7.3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.27</v>
+        <v>1.03</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.56</v>
+        <v>2.17</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.9</v>
+        <v>1.95</v>
       </c>
       <c r="AX30" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.82</v>
+        <v>1.38</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BA30" t="n">
         <v>4.6</v>
       </c>
       <c r="BB30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.1</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.37</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.91</v>
+        <v>4.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="R31" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="S31" t="n">
-        <v>3.52</v>
+        <v>4.75</v>
       </c>
       <c r="T31" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="W31" t="n">
-        <v>3.75</v>
+        <v>2.53</v>
       </c>
       <c r="X31" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
         <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>5.2</v>
+        <v>3.01</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.19</v>
+        <v>3.77</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.67</v>
+        <v>6.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.04</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.69</v>
+        <v>1.75</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.69</v>
+        <v>2.23</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.3</v>
+        <v>3.34</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T33" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W33" t="n">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="X33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.98</v>
+        <v>2.95</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AF33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BD33" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="S34" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="T34" t="n">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="V34" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="W34" t="n">
-        <v>3.52</v>
+        <v>2.94</v>
       </c>
       <c r="X34" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL34" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AM34" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BC34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.77</v>
       </c>
-      <c r="BD34" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.95</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.7</v>
+        <v>2.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="S36" t="n">
-        <v>2.21</v>
+        <v>3.52</v>
       </c>
       <c r="T36" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="U36" t="n">
-        <v>4.54</v>
+        <v>2.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W36" t="n">
         <v>3.75</v>
       </c>
       <c r="X36" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA36" t="n">
         <v>1.13</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.04</v>
+        <v>5.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.85</v>
+        <v>3.67</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.39</v>
+        <v>2.69</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.06</v>
+        <v>1.35</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7902,124 +7902,124 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8174,13 +8174,13 @@
         <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8189,34 +8189,34 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8493,124 +8493,124 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9356,13 +9356,13 @@
         <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
         <v>0</v>
@@ -9371,34 +9371,34 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -10132,7 +10132,7 @@
         <v>1.18</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1007,55 +1007,55 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="T3" t="n">
         <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="X3" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="Y3" t="n">
         <v>1.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB3" t="n">
         <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AE3" t="n">
         <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="AH3" t="n">
         <v>1.35</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.54</v>
+        <v>5.53</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.09</v>
@@ -1067,10 +1067,10 @@
         <v>2.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1079,37 +1079,37 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU3" t="n">
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB3" t="n">
         <v>1.17</v>
@@ -1118,7 +1118,7 @@
         <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
         <v>1.75</v>
@@ -1198,76 +1198,76 @@
         <v>1.38</v>
       </c>
       <c r="Q4" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z4" t="n">
         <v>4.8</v>
       </c>
-      <c r="R4" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U4" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AA4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB4" t="n">
         <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.41</v>
+        <v>6.64</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.94</v>
+        <v>4.01</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AM4" t="n">
         <v>1.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -1294,34 +1294,34 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB4" t="n">
         <v>1.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>9.65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,52 +1473,52 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL8" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="AM8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT8" t="n">
         <v>2.7</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.64</v>
+        <v>1.99</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU13" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="AV13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
         <v>1.6</v>
       </c>
-      <c r="S13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>1.74</v>
-      </c>
       <c r="BD13" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.84</v>
+        <v>2.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>2.17</v>
+        <v>2.89</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.12</v>
+        <v>1.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AE14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.49</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>2</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>2.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>8.550000000000001</v>
+        <v>2.17</v>
       </c>
       <c r="S15" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>2.95</v>
       </c>
-      <c r="U15" t="n">
-        <v>7</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL15" t="n">
+      <c r="AW15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
         <v>2</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>2.17</v>
       </c>
       <c r="BF15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>9.800000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.35</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.36</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>2.13</v>
       </c>
       <c r="V16" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>4.4</v>
+        <v>3.28</v>
       </c>
       <c r="X16" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AB16" t="n">
         <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>6.75</v>
+        <v>4.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.05</v>
+        <v>2.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ16" t="n">
         <v>1.33</v>
       </c>
-      <c r="AK16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="BB16" t="n">
         <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.4</v>
+        <v>4.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.89</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL17" t="n">
         <v>2.06</v>
       </c>
-      <c r="U17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AM17" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.41</v>
+        <v>1.02</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,52 +3837,52 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.49</v>
+        <v>2.25</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3962,13 +3962,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>8.85</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>1.17</v>
@@ -3977,10 +3977,10 @@
         <v>4.4</v>
       </c>
       <c r="X18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z18" t="n">
         <v>3.6</v>
@@ -3995,19 +3995,19 @@
         <v>1.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AE18" t="n">
         <v>1.26</v>
       </c>
       <c r="AF18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AG18" t="n">
         <v>1.76</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AI18" t="n">
         <v>2.7</v>
@@ -4016,7 +4016,7 @@
         <v>1.38</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL18" t="n">
         <v>1.68</v>
@@ -4025,7 +4025,7 @@
         <v>1.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.61</v>
+        <v>2.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="R22" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="S22" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.25</v>
       </c>
-      <c r="T22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U22" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AB22" t="n">
         <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.84</v>
+        <v>4.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.16</v>
+        <v>1.56</v>
       </c>
       <c r="AF22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AG22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.32</v>
+        <v>4.7</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.5</v>
+        <v>1.97</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,97 +4938,97 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.87</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="S23" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="V23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="X23" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
         <v>5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD23" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.84</v>
+        <v>3.59</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.23</v>
       </c>
       <c r="AK23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU23" t="n">
         <v>0</v>
@@ -5037,34 +5037,34 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.23</v>
+        <v>1.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>5.75</v>
       </c>
       <c r="S24" t="n">
-        <v>2.79</v>
+        <v>1.78</v>
       </c>
       <c r="T24" t="n">
-        <v>2.29</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>3.44</v>
+        <v>4.05</v>
       </c>
       <c r="X24" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="Z24" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.33</v>
+        <v>6.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.69</v>
+        <v>2.28</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.54</v>
+        <v>2.97</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
@@ -5234,34 +5234,34 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="R25" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="S25" t="n">
-        <v>4.22</v>
+        <v>3.37</v>
       </c>
       <c r="T25" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W25" t="n">
-        <v>3.52</v>
+        <v>3.75</v>
       </c>
       <c r="X25" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AI25" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="S26" t="n">
-        <v>2.21</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>4.54</v>
+        <v>2.14</v>
       </c>
       <c r="V26" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="X26" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.04</v>
+        <v>6.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
@@ -5628,34 +5628,34 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q27" t="n">
         <v>3.4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3.8</v>
-      </c>
       <c r="R27" t="n">
-        <v>1.78</v>
+        <v>4.8</v>
       </c>
       <c r="S27" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="T27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U27" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
         <v>2.5</v>
       </c>
-      <c r="U27" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.25</v>
+        <v>3.32</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.11</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y28" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W28" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Z28" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
         <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.63</v>
+        <v>4.95</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.27</v>
+        <v>1.23</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,52 +6004,52 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU28" t="n">
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.36</v>
+        <v>3.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.6</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>5.75</v>
+        <v>2.22</v>
       </c>
       <c r="S29" t="n">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>5.95</v>
+        <v>2.7</v>
       </c>
       <c r="V29" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>3.98</v>
+        <v>3.1</v>
       </c>
       <c r="X29" t="n">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI29" t="n">
         <v>4.5</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AJ29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.16</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC29" t="n">
-        <v>1.59</v>
+        <v>1.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>4.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.29</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>4.45</v>
       </c>
       <c r="S30" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="U30" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="W30" t="n">
-        <v>2.53</v>
+        <v>3.44</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>2.31</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.34</v>
+        <v>1.56</v>
       </c>
       <c r="Z30" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.95</v>
+        <v>4.6</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>2.31</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.21</v>
+        <v>1.46</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.3</v>
+        <v>4.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.05</v>
+        <v>2.27</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.48</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.1</v>
+        <v>1.23</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>1.29</v>
       </c>
       <c r="Q33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>11</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U33" t="n">
+        <v>9</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X33" t="n">
         <v>3.2</v>
       </c>
-      <c r="R33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AD33" t="n">
         <v>2.95</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AH33" t="n">
         <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.25</v>
+        <v>7.3</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.82</v>
+        <v>1.47</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.52</v>
+        <v>3.05</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="R34" t="n">
-        <v>1.95</v>
+        <v>4.28</v>
       </c>
       <c r="S34" t="n">
-        <v>4.16</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U34" t="n">
-        <v>2.57</v>
+        <v>4.54</v>
       </c>
       <c r="V34" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>2.94</v>
+        <v>3.44</v>
       </c>
       <c r="X34" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.62</v>
+        <v>4.9</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.99</v>
+        <v>2.43</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AI34" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="AM34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BF34" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="U35" t="n">
-        <v>2.5</v>
+        <v>3.55</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>3.16</v>
+        <v>2.63</v>
       </c>
       <c r="X35" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.98</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AF35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>1.89</v>
-      </c>
       <c r="BD35" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.91</v>
+        <v>3.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="S36" t="n">
-        <v>3.52</v>
+        <v>4.53</v>
       </c>
       <c r="T36" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U36" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V36" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="W36" t="n">
-        <v>3.75</v>
+        <v>2.94</v>
       </c>
       <c r="X36" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AD36" t="n">
-        <v>5.2</v>
+        <v>3.62</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.19</v>
+        <v>2.6</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AI36" t="n">
-        <v>3.67</v>
+        <v>5.25</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="AM36" t="n">
         <v>1.26</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7580,52 +7580,52 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.69</v>
+        <v>1.98</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7902,124 +7902,124 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4.39</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S39" t="n">
-        <v>3.73</v>
+        <v>4.4</v>
       </c>
       <c r="T39" t="n">
         <v>2.49</v>
@@ -8114,13 +8114,13 @@
         <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA39" t="n">
         <v>1.14</v>
@@ -8129,28 +8129,28 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.74</v>
+        <v>2.48</v>
       </c>
       <c r="AG39" t="n">
         <v>2.17</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK39" t="n">
         <v>1.48</v>
@@ -8162,7 +8162,7 @@
         <v>1.18</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>1.43</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8690,124 +8690,124 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9863,67 +9863,67 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.11</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="T48" t="n">
         <v>2.3</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W48" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X48" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z48" t="n">
         <v>6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.95</v>
+        <v>5.3</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK48" t="n">
         <v>1.75</v>
@@ -9932,10 +9932,10 @@
         <v>1.95</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AN48" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10075,7 +10075,7 @@
         <v>2.26</v>
       </c>
       <c r="U49" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V49" t="n">
         <v>1.3</v>
@@ -10105,19 +10105,19 @@
         <v>3.74</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AF49" t="n">
         <v>2.01</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="AH49" t="n">
         <v>1.37</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AJ49" t="n">
         <v>1.13</v>
@@ -10475,13 +10475,13 @@
         <v>1.33</v>
       </c>
       <c r="W51" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="X51" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="Z51" t="n">
         <v>6.5</v>
@@ -10514,7 +10514,7 @@
         <v>6</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK51" t="n">
         <v>1.73</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.83</v>
+        <v>4.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>2.17</v>
+        <v>1.61</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2.45</v>
       </c>
-      <c r="U15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.55</v>
+        <v>2.21</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3446,49 +3446,49 @@
         <v>1.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AX15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC15" t="n">
         <v>1.78</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE15" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.46</v>
+        <v>2.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.61</v>
       </c>
-      <c r="S16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.55</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.08</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3643,49 +3643,49 @@
         <v>1.33</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.45</v>
+        <v>2.23</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.93</v>
+        <v>3.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="R22" t="n">
-        <v>2.22</v>
+        <v>1.78</v>
       </c>
       <c r="S22" t="n">
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="T22" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="X22" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="Z22" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AD22" t="n">
-        <v>4.5</v>
+        <v>6.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
         <v>1.44</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4825,13 +4825,13 @@
         <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
@@ -4840,34 +4840,34 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.48</v>
+        <v>2.95</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Pyramids FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>1.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>3.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>3.58</v>
+        <v>10</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>3.44</v>
+        <v>2.53</v>
       </c>
       <c r="X23" t="n">
-        <v>2.14</v>
+        <v>3.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.31</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.36</v>
+        <v>3.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>5.75</v>
+        <v>1.92</v>
       </c>
       <c r="S24" t="n">
-        <v>1.78</v>
+        <v>4.53</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="U24" t="n">
-        <v>6</v>
+        <v>2.43</v>
       </c>
       <c r="V24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.18</v>
       </c>
-      <c r="W24" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BC24" t="n">
-        <v>1.59</v>
+        <v>1.98</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.52</v>
       </c>
       <c r="R26" t="n">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="S26" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W26" t="n">
         <v>3.75</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.2</v>
-      </c>
       <c r="X26" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>6.26</v>
+        <v>5.15</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
         <v>1.39</v>
       </c>
-      <c r="AF26" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY26" t="n">
         <v>1.72</v>
       </c>
-      <c r="AI26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AZ26" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="BB26" t="n">
         <v>1.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="BD26" t="n">
         <v>5.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.61</v>
+        <v>3.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="S27" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>6.53</v>
+        <v>2.7</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.84</v>
+        <v>3.92</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="AI27" t="n">
-        <v>8.1</v>
+        <v>4.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.85</v>
+        <v>1.54</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.58</v>
+        <v>2.95</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.5</v>
+        <v>2.28</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.32</v>
+        <v>4.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Strømmen</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,28 +5923,28 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.4</v>
+        <v>2.93</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="R28" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="S28" t="n">
-        <v>4.17</v>
+        <v>3.41</v>
       </c>
       <c r="T28" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="V28" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="X28" t="n">
         <v>2.25</v>
@@ -5956,46 +5956,46 @@
         <v>5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AB28" t="n">
         <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AI28" t="n">
-        <v>4</v>
+        <v>3.84</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6004,52 +6004,52 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AT28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>2.25</v>
       </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.33</v>
-      </c>
       <c r="BA28" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.95</v>
+        <v>4.7</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.01</v>
+        <v>1.71</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W29" t="n">
         <v>3.44</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W29" t="n">
-        <v>3.1</v>
-      </c>
       <c r="X29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AL29" t="n">
         <v>2.39</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.35</v>
+        <v>2.06</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6204,13 +6204,13 @@
         <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AU29" t="n">
         <v>0</v>
@@ -6219,34 +6219,34 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.67</v>
+        <v>2.43</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W30" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.59</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W30" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BD30" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Strømmen</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S32" t="n">
-        <v>4.75</v>
+        <v>4.17</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.52</v>
       </c>
       <c r="U32" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="V32" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>2.53</v>
+        <v>3.52</v>
       </c>
       <c r="X32" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AB32" t="n">
         <v>1.02</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.01</v>
+        <v>4.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.77</v>
+        <v>2.28</v>
       </c>
       <c r="AH32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pyramids FC</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.29</v>
+        <v>4.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.3</v>
+        <v>3.24</v>
       </c>
       <c r="R33" t="n">
-        <v>11</v>
+        <v>1.8</v>
       </c>
       <c r="S33" t="n">
-        <v>1.83</v>
+        <v>5.17</v>
       </c>
       <c r="T33" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>2.45</v>
       </c>
       <c r="V33" t="n">
         <v>1.43</v>
@@ -6932,109 +6932,109 @@
         <v>2.53</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA33" t="n">
         <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.7</v>
+        <v>3.77</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.64</v>
+        <v>1.89</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="BA33" t="n">
-        <v>4.6</v>
+        <v>1.52</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BC33" t="n">
         <v>2.24</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.48</v>
+        <v>3.34</v>
       </c>
       <c r="BE33" t="n">
         <v>1.57</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="R34" t="n">
-        <v>4.28</v>
+        <v>4.45</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="T34" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="U34" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="V34" t="n">
         <v>1.24</v>
@@ -7129,55 +7129,55 @@
         <v>3.44</v>
       </c>
       <c r="X34" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC34" t="n">
         <v>1.13</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.39</v>
+        <v>2.18</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.06</v>
+        <v>2.27</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>1.77</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
@@ -7213,25 +7213,25 @@
         <v>1.58</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BB34" t="n">
         <v>1.12</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,79 +7499,79 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.6</v>
+        <v>2.14</v>
       </c>
       <c r="Q36" t="n">
         <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="S36" t="n">
-        <v>4.53</v>
+        <v>2.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="U36" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W36" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF36" t="n">
         <v>2.43</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="X36" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.99</v>
-      </c>
       <c r="AG36" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AI36" t="n">
-        <v>5.25</v>
+        <v>3.59</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7580,52 +7580,52 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AU36" t="n">
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
         <v>2.55</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7902,124 +7902,124 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="T39" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="U39" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="V39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.2</v>
       </c>
-      <c r="W39" t="n">
-        <v>4</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AD39" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.61</v>
+        <v>4.25</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AM39" t="n">
         <v>1.18</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW39" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.28</v>
+        <v>1.65</v>
       </c>
       <c r="AY39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.85</v>
       </c>
-      <c r="AZ39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8371,13 +8371,13 @@
         <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU40" t="n">
         <v>0</v>
@@ -8386,34 +8386,34 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8690,124 +8690,124 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Angel City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Angel City</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G54" t="n">

--- a/jogos_2026-05-20.xlsx
+++ b/jogos_2026-05-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.65</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1473,52 +1473,52 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.66</v>
+        <v>3.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
-        <v>3.44</v>
+        <v>2.84</v>
       </c>
       <c r="X7" t="n">
-        <v>2.23</v>
+        <v>2.84</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AY7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Meshakhte</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2613,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2810,40 +2810,40 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>4.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="S13" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>2.13</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS13" t="n">
         <v>1.95</v>
       </c>
-      <c r="Y13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AT13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU13" t="n">
         <v>4</v>
       </c>
-      <c r="AA13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE13" t="n">
+      <c r="AV13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BA13" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="AG14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK14" t="n">
         <v>1.41</v>
       </c>
-      <c r="W14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL14" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.28</v>
+        <v>1.7</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.49</v>
+        <v>2</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>2.89</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.13</v>
+        <v>3.4</v>
       </c>
       <c r="V15" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
         <v>2.28</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BD15" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.92</v>
+        <v>1.49</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,100 +3559,100 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.83</v>
+        <v>9.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>1.56</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.8</v>
+        <v>6.95</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.4</v>
+        <v>3.12</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
         <v>2.95</v>
@@ -3667,25 +3667,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.23</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.81</v>
+        <v>1.23</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
         <v>7</v>
       </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.56</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.92<